--- a/public/files/Data_By_Towns_Index/Camden/Bellmawr Borough.xlsx
+++ b/public/files/Data_By_Towns_Index/Camden/Bellmawr Borough.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,28 +425,1302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E1"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Owner Name</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AMIN JITENDRA &amp; KALPANA J</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>208 CREEK RD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-75.0882852</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.866259</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJjV8E417OxokRomjHoIXvrnY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATEL ASHOK A &amp; ALKABEN A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>224 W BROWNING RD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-75.08892829999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.8670446</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJzx-OIl_OxokRURc3K0SbY-U</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATEL GAURANG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>299 MEYNER DR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-75.0946931</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.867163</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJjQFjtVnOxokRmaZP3ejUR60</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PATEL SANOLI R</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>301 COLONIAL RD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-75.0950242</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.8677769</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJD-bWNljOxokRth5RB_SMFlg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PATEL DIPIKABEN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27 W CHESTNUT AVE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-75.0813048</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.8671916</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJmf9AzGHOxokRcD-EM33JNcg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PATEL KETAN &amp; PRITIBEN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30 CHADWICK AVE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-75.0777698</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39.8653846</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJ4yKHMWLOxokR5YoJJMXlMMw</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PATEL JAYESH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27 CHADWICK AVE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-75.0773634</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39.865548</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJlRwKN2LOxokRgM6Lelnwjbk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PATEL RAMANBHAI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35 CURTIS AVE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-75.07605029999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.8675421</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJCd4x1InOxokRrMLwTPvvzjc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PATEL DAXESHKUMAR &amp; JAYSHREEBEN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23 BRAISINGTON AVE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-75.07484839999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.8674366</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ChIJGeRdJojOxokRFbc4XkRw1yM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PATEL JEMINI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>116 GLENVIEW AVE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>-75.0744316</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39.8676774</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ChIJydnOIojOxokRI1yT0pUxPd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PATEL ATUL &amp; ANILA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>201 THIRD AVE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>-75.07317259999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39.8666914</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ChIJnbj9q2LOxokRZR1XHF9pLsE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PATEL DHARMESH &amp; JAYSHRI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>139 E BROWNING RD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>-75.07395679999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.8657082</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ChIJv5DFwGLOxokRb8d2A9iLL24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PATEL ANKITA D</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>57 EVERGREEN AVE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>-75.07154969999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.8672854</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ChIJNSJa8ofOxokRJQgyJCmy7PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PATEL VIJAY N &amp; YOGINI V</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>245 SPRUCE AVENUE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-75.07207919999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>39.8681323</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ChIJESlN3YfOxokRsxsOdDHOf74</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PATEL SANJAY R &amp; RITABEN S</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>241 SPRUCE AVENUE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>-75.0723045</v>
+      </c>
+      <c r="G16" t="n">
+        <v>39.8680448</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ChIJz-5y54fOxokRe_XoLIfETlI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PATEL, PARTH &amp; DIPALI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>237 SPRUCE AVENUE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>-75.0725772</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.8679616</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ChIJgcsR4YfOxokRG27f7K5NenU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PATEL BHOGILAL T &amp; BHARATIBE B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>105 GRAFTON AVENUE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>-75.07272709999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39.8681893</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ChIJS7Lg34fOxokRlGYvcdQMlgs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PATEL VINESH A &amp; NAMITABEN V</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>130 DEVON AVE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>-75.0724913</v>
+      </c>
+      <c r="G19" t="n">
+        <v>39.8690728</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ChIJc_Wo1ofOxokRiKM9Lf3Smhg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SHAH KAMLESH D &amp; SONIYA K</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>313 BRADLEY AVE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>-75.0729669</v>
+      </c>
+      <c r="G20" t="n">
+        <v>39.8694728</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ChIJK4p4gIjOxokRnbN6Mjqtw8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PATEL KETAN R &amp; BHAVNABEN K</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>309 BRADLEY AVE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>-75.0731782</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39.8693693</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ChIJBTd4fojOxokRJMx2tMSFYMc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PATEL BHAVIN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>67 BRAISINGTON AVE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>-75.075897</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39.8689244</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ChIJNZx_s4nOxokROfFlnVFFN-M</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PATEL RAKESHKUMAR R &amp; MEGHABEN R</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>71 BRAISINGTON AVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>-75.07603189999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>39.869071</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ChIJYbTTs4nOxokRoUyfHuTU_yA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PATEL CHHAYA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>68 E CHESTNUT AVE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>-75.0768157</v>
+      </c>
+      <c r="G24" t="n">
+        <v>39.8683231</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ChIJzQsNxInOxokRVdcfVwrSHG0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PATEL JAYESH &amp; PRITI &amp; SHASHANK &amp;</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>60 E CHESTNUT AVE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>-75.07723179999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39.868216</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ChIJ1-k96InOxokRCOvWBcohFJI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PATEL VIPULKUMAR P &amp; ARPITA V</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>292 E BROWNING ROAD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>-75.0695059</v>
+      </c>
+      <c r="G26" t="n">
+        <v>39.8651735</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ChIJu-n1oX3OxokRIxrdQoRTd1E</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PATEL VIRENDRABHAI &amp; DAXABEN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>314 E BROWNING RD</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>-75.06849729999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>39.8654592</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ChIJQw9Sk33OxokRA5hY8E_Rba0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PATEL MAITRI &amp; SUNIL BHAGUBHAI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>317 OAKLAND AVE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>-75.06777289999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>39.8644221</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ChIJ421ExX3OxokRjKyDXLqKeCs</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PATEL DHANESHKUMAR &amp; VIMALBEN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>321 CHESTER AVE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>-75.06710339999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>39.8637381</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ChIJNbUi1X3OxokRSy3LG4GaVuI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PATEL THAKORBHAI D &amp; MINAKSHIBAHEN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>73 S BELLMAWR AVENUE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>-75.06585269999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>39.8635811</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ChIJuW6LYX7OxokRdPUWv_zbaWY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PATEL NEIL B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>132 S CEDAR AVE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>-75.06300829999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>39.862512</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ChIJZ3ARDn_OxokRd7SDLFfTcX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PATEL GIRISHKUMAR S &amp; VAUBHAV &amp; S</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>532 LINCOLN AVE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>-75.06178079999999</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39.8641296</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ChIJfxlpjX_OxokRaBWS3tFrzzc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PATEL GARGI &amp; ASHOK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>436 SECOND AVE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>-75.06619069999999</v>
+      </c>
+      <c r="G33" t="n">
+        <v>39.8678984</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ChIJCRlbxYDOxokRjSOlVc80l2Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SHAH SANJAY &amp; ALPA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>436 THIRD AVE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bellmawr Borough</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>-75.0665762</v>
+      </c>
+      <c r="G34" t="n">
+        <v>39.8686574</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ChIJj5r5KYHOxokREAI0SlfJFWE</t>
         </is>
       </c>
     </row>
